--- a/data/trans_camb/P12_2_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 14,33</t>
+          <t>0,02; 14,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 15,57</t>
+          <t>0,69; 14,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 9,37</t>
+          <t>-4,05; 9,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 18,57</t>
+          <t>3,84; 19,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 25,12</t>
+          <t>9,35; 25,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 20,83</t>
+          <t>6,87; 20,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 14,86</t>
+          <t>4,41; 15,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 18,34</t>
+          <t>6,86; 17,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 12,99</t>
+          <t>2,95; 13,32</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 86,04</t>
+          <t>-0,03; 89,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 96,88</t>
+          <t>2,06; 89,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 57,17</t>
+          <t>-18,04; 59,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 111,19</t>
+          <t>15,19; 118,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,67; 149,48</t>
+          <t>38,43; 148,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,62; 129,24</t>
+          <t>26,83; 119,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 82,06</t>
+          <t>18,73; 83,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,52; 105,01</t>
+          <t>28,51; 96,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 74,17</t>
+          <t>12,47; 74,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -8,98</t>
+          <t>-18,89; -8,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,62; -5,52</t>
+          <t>-15,57; -5,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -7,99</t>
+          <t>-17,61; -7,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,2; -9,76</t>
+          <t>-21,01; -10,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,75; -8,56</t>
+          <t>-20,29; -9,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -10,13</t>
+          <t>-20,01; -9,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -11,2</t>
+          <t>-17,97; -10,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,48; -9,04</t>
+          <t>-16,51; -8,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,29; -10,14</t>
+          <t>-17,36; -10,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-70,24; -40,32</t>
+          <t>-70,63; -39,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,04; -25,69</t>
+          <t>-58,31; -28,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,02; -36,96</t>
+          <t>-67,81; -36,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,06; -32,18</t>
+          <t>-56,91; -33,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,08; -28,67</t>
+          <t>-55,66; -30,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,36; -33,48</t>
+          <t>-54,55; -32,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,27; -41,83</t>
+          <t>-59,86; -40,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,21; -33,67</t>
+          <t>-53,21; -32,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -38,78</t>
+          <t>-56,89; -39,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 8,86</t>
+          <t>-1,5; 9,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,37</t>
+          <t>3,92; 15,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 10,26</t>
+          <t>-0,43; 9,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,84</t>
+          <t>-6,44; 5,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 9,91</t>
+          <t>-2,73; 10,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 1,52</t>
+          <t>-9,65; 1,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,5</t>
+          <t>-2,7; 5,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,76</t>
+          <t>1,76; 10,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 4,32</t>
+          <t>-3,65; 4,12</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 102,64</t>
+          <t>-12,43; 104,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,02; 179,46</t>
+          <t>22,77; 164,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 114,95</t>
+          <t>-4,55; 107,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 33,56</t>
+          <t>-28,23; 31,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 54,13</t>
+          <t>-11,71; 60,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,43; 9,3</t>
+          <t>-39,21; 8,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 38,21</t>
+          <t>-14,89; 39,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,46; 75,24</t>
+          <t>9,45; 72,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 30,74</t>
+          <t>-19,8; 30,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 10,58</t>
+          <t>-0,37; 10,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 12,42</t>
+          <t>1,69; 12,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 11,49</t>
+          <t>-1,01; 10,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 18,97</t>
+          <t>5,04; 18,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 7,04</t>
+          <t>-6,28; 7,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,69; -2,82</t>
+          <t>-17,93; -2,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,99</t>
+          <t>4,04; 13,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,84</t>
+          <t>-0,68; 7,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 2,12</t>
+          <t>-9,19; 1,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 96,37</t>
+          <t>-2,46; 92,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 105,0</t>
+          <t>9,29; 112,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 100,47</t>
+          <t>-8,21; 96,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,95; 80,6</t>
+          <t>16,62; 78,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 30,51</t>
+          <t>-21,59; 30,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,22; -12,7</t>
+          <t>-62,09; -11,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,51; 69,17</t>
+          <t>17,39; 72,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 42,08</t>
+          <t>-3,5; 41,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,61; 11,1</t>
+          <t>-40,75; 8,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-27,15; -10,16</t>
+          <t>-25,99; -9,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,38; -3,4</t>
+          <t>-20,67; -3,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 13,04</t>
+          <t>-5,06; 13,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -2,18</t>
+          <t>-20,49; -1,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,08; -8,19</t>
+          <t>-26,62; -7,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 15,73</t>
+          <t>-0,56; 15,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-21,29; -8,22</t>
+          <t>-20,98; -7,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-20,84; -8,22</t>
+          <t>-21,12; -8,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 12,91</t>
+          <t>-0,43; 12,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,38; -32,94</t>
+          <t>-67,91; -32,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,04; -10,26</t>
+          <t>-54,62; -12,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 44,91</t>
+          <t>-12,32; 47,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,07; -4,9</t>
+          <t>-41,7; -2,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,03; -20,54</t>
+          <t>-53,74; -18,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 41,12</t>
+          <t>-0,83; 40,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,27; -23,14</t>
+          <t>-49,17; -22,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,05; -22,72</t>
+          <t>-49,59; -23,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,8; 35,87</t>
+          <t>-0,94; 34,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 8,08</t>
+          <t>-3,47; 8,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 6,04</t>
+          <t>-4,99; 6,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 9,34</t>
+          <t>-1,57; 9,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,98; -3,82</t>
+          <t>-16,25; -2,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -2,21</t>
+          <t>-16,16; -2,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,64; -5,86</t>
+          <t>-19,16; -6,12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 0,4</t>
+          <t>-8,51; 0,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,25; -0,12</t>
+          <t>-9,22; 0,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 0,43</t>
+          <t>-8,04; -0,1</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 82,81</t>
+          <t>-23,6; 91,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 69,06</t>
+          <t>-33,43; 70,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 101,63</t>
+          <t>-10,3; 105,03</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-55,53; -15,28</t>
+          <t>-52,69; -12,8</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-53,75; -9,42</t>
+          <t>-52,12; -7,84</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,44; -24,07</t>
+          <t>-58,88; -25,95</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 2,95</t>
+          <t>-38,33; 2,95</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -0,71</t>
+          <t>-40,61; 0,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 2,61</t>
+          <t>-36,02; -1,14</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,53; 14,18</t>
+          <t>6,11; 14,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,18</t>
+          <t>2,22; 9,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,65</t>
+          <t>5,11; 13,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 8,22</t>
+          <t>-1,59; 7,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,9</t>
+          <t>-3,36; 6,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 5,28</t>
+          <t>-14,62; 4,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,65</t>
+          <t>3,12; 9,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,13</t>
+          <t>0,78; 6,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 7,67</t>
+          <t>-3,84; 7,81</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>47,9; 169,84</t>
+          <t>48,58; 165,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20,28; 116,94</t>
+          <t>18,0; 111,39</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42,19; 157,97</t>
+          <t>40,68; 156,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 40,3</t>
+          <t>-6,38; 38,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 28,7</t>
+          <t>-13,47; 29,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-56,34; 24,15</t>
+          <t>-57,48; 22,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,32; 63,31</t>
+          <t>16,66; 63,84</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,47; 47,64</t>
+          <t>3,07; 45,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 48,07</t>
+          <t>-21,12; 48,64</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-16,07; -7,63</t>
+          <t>-16,42; -7,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-25,62; -18,41</t>
+          <t>-26,13; -18,48</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-27,14; -16,99</t>
+          <t>-27,45; -16,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-18,47; -8,9</t>
+          <t>-17,68; -8,31</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-27,98; -19,22</t>
+          <t>-28,08; -19,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-23,62; -14,79</t>
+          <t>-23,69; -15,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-15,88; -9,56</t>
+          <t>-15,9; -9,53</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-26,04; -20,17</t>
+          <t>-25,84; -20,08</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,81; -17,75</t>
+          <t>-26,65; -17,4</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-51,03; -27,67</t>
+          <t>-51,79; -27,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-81,34; -67,83</t>
+          <t>-81,49; -67,91</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-88,36; -60,38</t>
+          <t>-87,98; -60,11</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-46,24; -25,33</t>
+          <t>-45,19; -24,44</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-70,19; -54,78</t>
+          <t>-70,54; -55,07</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-58,85; -42,57</t>
+          <t>-58,36; -42,52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-45,1; -29,85</t>
+          <t>-45,24; -29,47</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-73,75; -63,07</t>
+          <t>-73,24; -63,1</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,95; -54,52</t>
+          <t>-76,12; -53,59</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,38</t>
+          <t>-4,04; -0,2</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,84</t>
+          <t>-5,67; -2,05</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -1,68</t>
+          <t>-7,08; -1,59</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -2,09</t>
+          <t>-6,44; -2,09</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -5,27</t>
+          <t>-9,75; -5,35</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-12,64; -5,64</t>
+          <t>-12,25; -5,71</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -1,68</t>
+          <t>-4,66; -1,7</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -4,05</t>
+          <t>-7,15; -4,23</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -4,11</t>
+          <t>-8,26; -3,95</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -2,06</t>
+          <t>-20,0; -1,33</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-27,63; -9,85</t>
+          <t>-27,6; -11,07</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,83; -8,84</t>
+          <t>-36,18; -8,34</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-20,78; -7,32</t>
+          <t>-20,95; -7,27</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-31,2; -18,31</t>
+          <t>-31,61; -18,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-42,08; -19,56</t>
+          <t>-40,38; -19,91</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,15; -6,93</t>
+          <t>-18,28; -7,1</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-27,67; -16,88</t>
+          <t>-28,02; -17,69</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -17,27</t>
+          <t>-33,13; -16,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_2_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,74</t>
+          <t>14,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,1</t>
+          <t>9,94</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 14,55</t>
+          <t>-0,03; 14,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 14,83</t>
+          <t>0,55; 15,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 9,71</t>
+          <t>-2,39; 11,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 19,42</t>
+          <t>3,0; 19,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 25,19</t>
+          <t>9,16; 24,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 20,68</t>
+          <t>8,03; 21,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,07</t>
+          <t>3,46; 14,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 17,48</t>
+          <t>7,27; 17,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 13,32</t>
+          <t>5,05; 15,02</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 89,07</t>
+          <t>-1,56; 85,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 89,13</t>
+          <t>0,22; 92,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 59,33</t>
+          <t>-9,83; 67,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,19; 118,3</t>
+          <t>11,97; 113,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,43; 148,71</t>
+          <t>36,26; 144,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,83; 119,48</t>
+          <t>32,26; 129,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,73; 83,97</t>
+          <t>14,34; 80,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,51; 96,47</t>
+          <t>30,3; 100,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,47; 74,76</t>
+          <t>21,73; 84,42</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-12,69</t>
+          <t>-12,52</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-15,08</t>
+          <t>-15,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-13,95</t>
+          <t>-13,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,89; -8,42</t>
+          <t>-18,54; -8,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,57; -5,98</t>
+          <t>-15,69; -5,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,61; -7,74</t>
+          <t>-17,37; -7,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -10,39</t>
+          <t>-20,47; -9,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -9,44</t>
+          <t>-19,9; -8,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,01; -9,99</t>
+          <t>-19,95; -9,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,97; -10,69</t>
+          <t>-18,17; -10,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -8,83</t>
+          <t>-16,33; -8,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -10,46</t>
+          <t>-17,33; -10,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-54,14%</t>
+          <t>-53,41%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-44,94%</t>
+          <t>-44,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-48,87%</t>
+          <t>-48,27%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-70,63; -39,22</t>
+          <t>-70,77; -42,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,31; -28,09</t>
+          <t>-59,96; -28,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,81; -36,06</t>
+          <t>-66,55; -35,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,91; -33,38</t>
+          <t>-56,82; -31,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,66; -30,08</t>
+          <t>-54,62; -28,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,55; -32,72</t>
+          <t>-54,88; -32,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,86; -40,17</t>
+          <t>-59,52; -40,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,21; -32,41</t>
+          <t>-53,28; -32,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,89; -39,11</t>
+          <t>-56,31; -39,21</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,82</t>
+          <t>-3,9</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 9,27</t>
+          <t>-1,67; 9,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 15,06</t>
+          <t>4,09; 14,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 9,59</t>
+          <t>-0,04; 9,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 5,66</t>
+          <t>-6,76; 5,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 10,38</t>
+          <t>-2,56; 10,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 1,37</t>
+          <t>-9,63; 1,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 5,73</t>
+          <t>-2,45; 5,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,56</t>
+          <t>1,83; 10,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 4,12</t>
+          <t>-3,16; 3,89</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-18,32%</t>
+          <t>-18,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 104,88</t>
+          <t>-13,45; 106,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,77; 164,57</t>
+          <t>24,82; 171,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 107,5</t>
+          <t>-1,7; 113,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 31,04</t>
+          <t>-28,79; 31,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 60,24</t>
+          <t>-10,97; 56,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 8,84</t>
+          <t>-38,8; 8,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 39,65</t>
+          <t>-13,44; 39,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 72,08</t>
+          <t>9,28; 75,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 30,47</t>
+          <t>-16,89; 27,07</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,81</t>
+          <t>-5,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-0,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 10,58</t>
+          <t>-0,47; 10,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 12,67</t>
+          <t>0,99; 12,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 10,86</t>
+          <t>-2,1; 10,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 18,51</t>
+          <t>5,47; 18,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 7,13</t>
+          <t>-5,78; 7,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,93; -2,89</t>
+          <t>-11,37; 0,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,02</t>
+          <t>4,5; 13,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 7,78</t>
+          <t>-0,83; 7,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 1,46</t>
+          <t>-4,75; 3,7</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-36,38%</t>
+          <t>-20,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-13,64%</t>
+          <t>-4,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 92,88</t>
+          <t>-3,04; 98,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,29; 112,57</t>
+          <t>5,64; 115,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 96,68</t>
+          <t>-13,59; 91,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,62; 78,79</t>
+          <t>17,8; 79,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 30,2</t>
+          <t>-19,67; 32,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,09; -11,89</t>
+          <t>-37,1; 4,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,39; 72,64</t>
+          <t>20,18; 73,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 41,57</t>
+          <t>-3,63; 43,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,75; 8,06</t>
+          <t>-22,01; 20,06</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>6,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>5,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,99; -9,68</t>
+          <t>-25,68; -9,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,67; -3,43</t>
+          <t>-20,66; -3,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 13,43</t>
+          <t>-5,14; 12,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,49; -1,43</t>
+          <t>-21,24; -1,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,62; -7,48</t>
+          <t>-26,95; -7,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 15,5</t>
+          <t>-2,26; 15,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-20,98; -7,82</t>
+          <t>-20,78; -7,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,12; -8,3</t>
+          <t>-20,53; -8,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 12,17</t>
+          <t>-0,94; 11,24</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,91; -32,96</t>
+          <t>-67,28; -31,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,62; -12,55</t>
+          <t>-53,88; -11,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 47,03</t>
+          <t>-13,08; 44,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,7; -2,93</t>
+          <t>-42,55; -4,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,74; -18,49</t>
+          <t>-53,43; -19,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 40,54</t>
+          <t>-4,85; 41,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,17; -22,33</t>
+          <t>-48,87; -21,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,59; -23,38</t>
+          <t>-48,98; -22,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 34,71</t>
+          <t>-2,79; 31,75</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-11,94</t>
+          <t>-11,91</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>-4,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 8,53</t>
+          <t>-3,42; 8,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 6,3</t>
+          <t>-5,14; 5,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 9,93</t>
+          <t>-1,5; 8,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -2,83</t>
+          <t>-17,15; -3,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -2,04</t>
+          <t>-17,17; -2,27</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -6,12</t>
+          <t>-17,44; -5,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 0,45</t>
+          <t>-8,3; 0,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 0,07</t>
+          <t>-9,26; 0,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -0,1</t>
+          <t>-8,52; -0,25</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-43,06%</t>
+          <t>-42,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-19,71%</t>
+          <t>-20,75%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 91,21</t>
+          <t>-23,07; 88,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,43; 70,52</t>
+          <t>-34,05; 57,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 105,03</t>
+          <t>-10,04; 97,81</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-52,69; -12,8</t>
+          <t>-54,46; -13,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,12; -7,84</t>
+          <t>-53,18; -9,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-58,88; -25,95</t>
+          <t>-56,74; -24,99</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 2,95</t>
+          <t>-37,64; 3,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 0,95</t>
+          <t>-40,79; 1,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-36,02; -1,14</t>
+          <t>-37,45; -1,65</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>9,15</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>6,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,11; 14,22</t>
+          <t>5,33; 13,98</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,96</t>
+          <t>2,87; 10,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,51</t>
+          <t>5,22; 14,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 7,95</t>
+          <t>-1,87; 7,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 6,0</t>
+          <t>-3,37; 5,96</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 4,96</t>
+          <t>-0,7; 8,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,84</t>
+          <t>3,17; 9,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,94</t>
+          <t>0,74; 7,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 7,81</t>
+          <t>3,57; 9,82</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-11,77%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>48,58; 165,48</t>
+          <t>42,01; 157,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>18,0; 111,39</t>
+          <t>21,53; 118,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40,68; 156,76</t>
+          <t>41,93; 162,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 38,84</t>
+          <t>-7,51; 38,38</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 29,56</t>
+          <t>-13,52; 29,12</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,48; 22,38</t>
+          <t>-2,81; 42,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,66; 63,84</t>
+          <t>17,73; 65,19</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,07; 45,15</t>
+          <t>3,77; 47,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 48,64</t>
+          <t>19,6; 65,15</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-21,47</t>
+          <t>-18,96</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-19,15</t>
+          <t>-19,72</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-21,08</t>
+          <t>-19,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-16,42; -7,6</t>
+          <t>-16,18; -7,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-26,13; -18,48</t>
+          <t>-26,15; -18,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-27,45; -16,81</t>
+          <t>-23,05; -14,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-17,68; -8,31</t>
+          <t>-18,56; -9,4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-28,08; -19,42</t>
+          <t>-28,11; -19,83</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-23,69; -15,04</t>
+          <t>-24,39; -15,73</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-15,9; -9,53</t>
+          <t>-16,19; -9,72</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -20,08</t>
+          <t>-25,61; -20,0</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,65; -17,4</t>
+          <t>-22,26; -16,24</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-73,08%</t>
+          <t>-64,53%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-51,13%</t>
+          <t>-52,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-62,89%</t>
+          <t>-57,78%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-51,79; -27,86</t>
+          <t>-51,36; -27,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-81,49; -67,91</t>
+          <t>-81,38; -67,73</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,98; -60,11</t>
+          <t>-71,47; -54,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -24,44</t>
+          <t>-46,44; -25,78</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-70,54; -55,07</t>
+          <t>-71,06; -55,77</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-58,36; -42,52</t>
+          <t>-60,0; -44,94</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-45,24; -29,47</t>
+          <t>-45,78; -30,45</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-73,24; -63,1</t>
+          <t>-73,14; -62,9</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-76,12; -53,59</t>
+          <t>-62,95; -51,78</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-3,75</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-8,16</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-4,39</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,2</t>
+          <t>-4,08; -0,29</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -2,05</t>
+          <t>-5,49; -2,1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -1,59</t>
+          <t>-4,47; -0,8</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -2,09</t>
+          <t>-6,3; -1,83</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -5,35</t>
+          <t>-9,5; -5,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -5,71</t>
+          <t>-8,29; -4,28</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,7</t>
+          <t>-4,82; -1,8</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -4,23</t>
+          <t>-7,12; -4,09</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-8,26; -3,95</t>
+          <t>-5,77; -3,06</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-19,23%</t>
+          <t>-13,47%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-27,5%</t>
+          <t>-20,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-24,13%</t>
+          <t>-17,78%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-20,0; -1,33</t>
+          <t>-20,14; -1,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-27,6; -11,07</t>
+          <t>-27,15; -11,27</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,18; -8,34</t>
+          <t>-21,9; -4,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-20,95; -7,27</t>
+          <t>-20,44; -6,43</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -18,72</t>
+          <t>-31,14; -18,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-40,38; -19,91</t>
+          <t>-26,83; -15,13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -7,1</t>
+          <t>-18,88; -7,51</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -17,69</t>
+          <t>-27,94; -17,02</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-33,13; -16,58</t>
+          <t>-22,62; -12,89</t>
         </is>
       </c>
     </row>
